--- a/Attachment_A_Q2.xlsx
+++ b/Attachment_A_Q2.xlsx
@@ -563,12 +563,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S226</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -647,12 +647,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S226</t>
+          <t>S113</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -731,7 +731,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S389</t>
+          <t>S395</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -815,12 +815,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S102</t>
+          <t>S390</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -854,7 +854,7 @@
         <v>-0</v>
       </c>
       <c r="M5" t="n">
-        <v>12000</v>
+        <v>-0</v>
       </c>
       <c r="N5" t="n">
         <v>-0</v>
@@ -899,7 +899,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S260</t>
+          <t>S150</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -983,16 +983,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S358</t>
+          <t>S401</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="D7" t="n">
         <v>-0</v>
@@ -1019,7 +1019,7 @@
         <v>-0</v>
       </c>
       <c r="L7" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="M7" t="n">
         <v>-0</v>
@@ -1040,10 +1040,10 @@
         <v>-0</v>
       </c>
       <c r="S7" t="n">
-        <v>4200</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>16200</v>
+        <v>-0</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
@@ -1052,10 +1052,10 @@
         <v>-0</v>
       </c>
       <c r="W7" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="X7" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
@@ -1067,12 +1067,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S219</t>
+          <t>S231</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1082,25 +1082,25 @@
         <v>-0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0</v>
+        <v>10200</v>
       </c>
       <c r="F8" t="n">
         <v>-0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0</v>
+        <v>4200</v>
       </c>
       <c r="H8" t="n">
         <v>-0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>4200</v>
       </c>
       <c r="J8" t="n">
         <v>-0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="L8" t="n">
         <v>-0</v>
@@ -1118,22 +1118,22 @@
         <v>-0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="R8" t="n">
         <v>-0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="T8" t="n">
-        <v>-0</v>
+        <v>4200</v>
       </c>
       <c r="U8" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="V8" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="W8" t="n">
         <v>-0</v>
@@ -1145,25 +1145,25 @@
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S079</t>
+          <t>S359</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16200</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="E9" t="n">
         <v>-0</v>
@@ -1178,16 +1178,16 @@
         <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="J9" t="n">
         <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="L9" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="M9" t="n">
         <v>-0</v>
@@ -1235,16 +1235,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S038</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="D10" t="n">
         <v>-0</v>
@@ -1253,19 +1253,19 @@
         <v>-0</v>
       </c>
       <c r="F10" t="n">
-        <v>-0</v>
+        <v>16200</v>
       </c>
       <c r="G10" t="n">
         <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="I10" t="n">
         <v>-0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0</v>
+        <v>10200</v>
       </c>
       <c r="K10" t="n">
         <v>-0</v>
@@ -1277,13 +1277,13 @@
         <v>-0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0</v>
+        <v>10200</v>
       </c>
       <c r="O10" t="n">
         <v>-0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>12000</v>
       </c>
       <c r="Q10" t="n">
         <v>-0</v>
@@ -1298,19 +1298,19 @@
         <v>-0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="V10" t="n">
-        <v>-0</v>
+        <v>4200</v>
       </c>
       <c r="W10" t="n">
         <v>-0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="Z10" t="n">
         <v>-0</v>
@@ -1319,28 +1319,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S214</t>
+          <t>S222</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="D11" t="n">
         <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="F11" t="n">
         <v>-0</v>
       </c>
       <c r="G11" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="H11" t="n">
         <v>-0</v>
@@ -1355,7 +1355,7 @@
         <v>-0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="M11" t="n">
         <v>-0</v>
@@ -1364,16 +1364,16 @@
         <v>-0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0</v>
+        <v>12000</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="Q11" t="n">
         <v>-0</v>
       </c>
       <c r="R11" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="S11" t="n">
         <v>-0</v>
@@ -1403,12 +1403,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S047</t>
+          <t>S383</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1487,12 +1487,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S026</t>
+          <t>S067</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1571,7 +1571,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S373</t>
+          <t>S081</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1589,16 +1589,16 @@
         <v>-0</v>
       </c>
       <c r="F14" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="G14" t="n">
         <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="J14" t="n">
         <v>-0</v>
@@ -1610,7 +1610,7 @@
         <v>-0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0</v>
+        <v>4200</v>
       </c>
       <c r="N14" t="n">
         <v>-0</v>
@@ -1622,7 +1622,7 @@
         <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="R14" t="n">
         <v>-0</v>
@@ -1631,13 +1631,13 @@
         <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0</v>
+        <v>12000</v>
       </c>
       <c r="U14" t="n">
-        <v>-0</v>
+        <v>10200</v>
       </c>
       <c r="V14" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="W14" t="n">
         <v>-0</v>
@@ -1646,7 +1646,7 @@
         <v>-0</v>
       </c>
       <c r="Y14" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="Z14" t="n">
         <v>-0</v>
@@ -1655,19 +1655,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S067</t>
+          <t>S079</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="E15" t="n">
         <v>-0</v>
@@ -1688,25 +1688,25 @@
         <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="L15" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="M15" t="n">
         <v>-0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="O15" t="n">
         <v>-0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="R15" t="n">
         <v>-0</v>
@@ -1730,16 +1730,16 @@
         <v>-0</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S051</t>
+          <t>S388</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S395</t>
+          <t>S339</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1907,12 +1907,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S028</t>
+          <t>S093</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1928,10 +1928,10 @@
         <v>-0</v>
       </c>
       <c r="G18" t="n">
-        <v>4200</v>
+        <v>-0</v>
       </c>
       <c r="H18" t="n">
-        <v>12000</v>
+        <v>-0</v>
       </c>
       <c r="I18" t="n">
         <v>-0</v>
@@ -1967,13 +1967,13 @@
         <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="U18" t="n">
         <v>-0</v>
       </c>
       <c r="V18" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="W18" t="n">
         <v>-0</v>
@@ -1991,28 +1991,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S286</t>
+          <t>S331</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>-0</v>
       </c>
       <c r="D19" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="E19" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="F19" t="n">
         <v>-0</v>
       </c>
       <c r="G19" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="H19" t="n">
         <v>-0</v>
@@ -2027,7 +2027,7 @@
         <v>-0</v>
       </c>
       <c r="L19" t="n">
-        <v>4200</v>
+        <v>-0</v>
       </c>
       <c r="M19" t="n">
         <v>-0</v>
@@ -2048,7 +2048,7 @@
         <v>-0</v>
       </c>
       <c r="S19" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="T19" t="n">
         <v>-0</v>
@@ -2075,22 +2075,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S240</t>
+          <t>S296</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>-0</v>
       </c>
       <c r="D20" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="E20" t="n">
-        <v>4200</v>
+        <v>-0</v>
       </c>
       <c r="F20" t="n">
         <v>-0</v>
@@ -2114,16 +2114,16 @@
         <v>-0</v>
       </c>
       <c r="M20" t="n">
-        <v>10200</v>
+        <v>-0</v>
       </c>
       <c r="N20" t="n">
         <v>-0</v>
       </c>
       <c r="O20" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="P20" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="Q20" t="n">
         <v>-0</v>
@@ -2150,7 +2150,7 @@
         <v>-0</v>
       </c>
       <c r="Y20" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="Z20" t="n">
         <v>-0</v>
@@ -2159,19 +2159,19 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S222</t>
+          <t>S097</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>-0</v>
       </c>
       <c r="D21" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="E21" t="n">
         <v>-0</v>
@@ -2183,13 +2183,13 @@
         <v>-0</v>
       </c>
       <c r="H21" t="n">
-        <v>4200</v>
+        <v>-0</v>
       </c>
       <c r="I21" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="J21" t="n">
-        <v>4200</v>
+        <v>-0</v>
       </c>
       <c r="K21" t="n">
         <v>-0</v>
@@ -2213,7 +2213,7 @@
         <v>-0</v>
       </c>
       <c r="R21" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="S21" t="n">
         <v>-0</v>
@@ -2222,10 +2222,10 @@
         <v>-0</v>
       </c>
       <c r="U21" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="V21" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="W21" t="n">
         <v>-0</v>
@@ -2234,7 +2234,7 @@
         <v>-0</v>
       </c>
       <c r="Y21" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="Z21" t="n">
         <v>-0</v>
@@ -2243,7 +2243,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S097</t>
+          <t>S341</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2327,12 +2327,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S207</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2411,16 +2411,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S310</t>
+          <t>S127</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0</v>
+        <v>10200</v>
       </c>
       <c r="D24" t="n">
         <v>-0</v>
@@ -2429,7 +2429,7 @@
         <v>-0</v>
       </c>
       <c r="F24" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="G24" t="n">
         <v>-0</v>
@@ -2438,16 +2438,16 @@
         <v>-0</v>
       </c>
       <c r="I24" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="J24" t="n">
         <v>-0</v>
       </c>
       <c r="K24" t="n">
-        <v>-0</v>
+        <v>4200</v>
       </c>
       <c r="L24" t="n">
-        <v>-0</v>
+        <v>12000</v>
       </c>
       <c r="M24" t="n">
         <v>-0</v>
@@ -2459,7 +2459,7 @@
         <v>-0</v>
       </c>
       <c r="P24" t="n">
-        <v>-0</v>
+        <v>4200</v>
       </c>
       <c r="Q24" t="n">
         <v>-0</v>
@@ -2468,7 +2468,7 @@
         <v>-0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0</v>
+        <v>16200</v>
       </c>
       <c r="T24" t="n">
         <v>-0</v>
@@ -2480,27 +2480,27 @@
         <v>-0</v>
       </c>
       <c r="W24" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="X24" t="n">
-        <v>-0</v>
+        <v>4200</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="Z24" t="n">
-        <v>-0</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S035</t>
+          <t>S184</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2546,19 +2546,19 @@
         <v>-0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4200</v>
+        <v>-0</v>
       </c>
       <c r="R25" t="n">
         <v>-0</v>
       </c>
       <c r="S25" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="T25" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="U25" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="V25" t="n">
         <v>-0</v>
@@ -2573,18 +2573,18 @@
         <v>-0</v>
       </c>
       <c r="Z25" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S323</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2597,7 +2597,7 @@
         <v>-0</v>
       </c>
       <c r="F26" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="G26" t="n">
         <v>-0</v>
@@ -2627,10 +2627,10 @@
         <v>-0</v>
       </c>
       <c r="P26" t="n">
-        <v>4200</v>
+        <v>-0</v>
       </c>
       <c r="Q26" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="R26" t="n">
         <v>-0</v>
@@ -2642,7 +2642,7 @@
         <v>-0</v>
       </c>
       <c r="U26" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="V26" t="n">
         <v>-0</v>
@@ -2654,7 +2654,7 @@
         <v>-0</v>
       </c>
       <c r="Y26" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="Z26" t="n">
         <v>-0</v>
@@ -2663,12 +2663,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S293</t>
+          <t>S165</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2678,7 +2678,7 @@
         <v>-0</v>
       </c>
       <c r="E27" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="F27" t="n">
         <v>-0</v>
@@ -2696,13 +2696,13 @@
         <v>-0</v>
       </c>
       <c r="K27" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="L27" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="M27" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="N27" t="n">
         <v>-0</v>
@@ -2741,13 +2741,13 @@
         <v>-0</v>
       </c>
       <c r="Z27" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S211</t>
+          <t>S225</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2831,12 +2831,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S119</t>
+          <t>S249</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2852,7 +2852,7 @@
         <v>-0</v>
       </c>
       <c r="G29" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="H29" t="n">
         <v>-0</v>
@@ -2864,7 +2864,7 @@
         <v>-0</v>
       </c>
       <c r="K29" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="L29" t="n">
         <v>-0</v>
@@ -2873,10 +2873,10 @@
         <v>-0</v>
       </c>
       <c r="N29" t="n">
-        <v>12000</v>
+        <v>-0</v>
       </c>
       <c r="O29" t="n">
-        <v>10200</v>
+        <v>-0</v>
       </c>
       <c r="P29" t="n">
         <v>-0</v>
@@ -2885,7 +2885,7 @@
         <v>-0</v>
       </c>
       <c r="R29" t="n">
-        <v>12000</v>
+        <v>-0</v>
       </c>
       <c r="S29" t="n">
         <v>-0</v>
@@ -2915,7 +2915,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S137</t>
+          <t>S116</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2999,7 +2999,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S199</t>
+          <t>S055</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3083,12 +3083,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S127</t>
+          <t>S261</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -3104,7 +3104,7 @@
         <v>-0</v>
       </c>
       <c r="G32" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="H32" t="n">
         <v>-0</v>
@@ -3113,7 +3113,7 @@
         <v>-0</v>
       </c>
       <c r="J32" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="K32" t="n">
         <v>-0</v>
@@ -3131,10 +3131,10 @@
         <v>-0</v>
       </c>
       <c r="P32" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="Q32" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="R32" t="n">
         <v>-0</v>
@@ -3149,7 +3149,7 @@
         <v>-0</v>
       </c>
       <c r="V32" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="W32" t="n">
         <v>-0</v>
@@ -3167,7 +3167,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S294</t>
+          <t>S345</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3251,7 +3251,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S372</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3263,7 +3263,7 @@
         <v>-0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0</v>
+        <v>10200</v>
       </c>
       <c r="E34" t="n">
         <v>-0</v>
@@ -3272,13 +3272,13 @@
         <v>-0</v>
       </c>
       <c r="G34" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="H34" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="I34" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="J34" t="n">
         <v>-0</v>
@@ -3287,7 +3287,7 @@
         <v>-0</v>
       </c>
       <c r="L34" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="M34" t="n">
         <v>-0</v>
@@ -3296,13 +3296,13 @@
         <v>-0</v>
       </c>
       <c r="O34" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="P34" t="n">
         <v>-0</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0</v>
+        <v>4200</v>
       </c>
       <c r="R34" t="n">
         <v>-0</v>
@@ -3311,7 +3311,7 @@
         <v>-0</v>
       </c>
       <c r="T34" t="n">
-        <v>-0</v>
+        <v>12000</v>
       </c>
       <c r="U34" t="n">
         <v>-0</v>
@@ -3326,7 +3326,7 @@
         <v>-0</v>
       </c>
       <c r="Y34" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="Z34" t="n">
         <v>-0</v>
@@ -3335,7 +3335,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S187</t>
+          <t>S177</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3347,25 +3347,25 @@
         <v>-0</v>
       </c>
       <c r="D35" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="E35" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="F35" t="n">
         <v>-0</v>
       </c>
       <c r="G35" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="H35" t="n">
-        <v>-0</v>
+        <v>4200</v>
       </c>
       <c r="I35" t="n">
         <v>-0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="K35" t="n">
         <v>-0</v>
@@ -3380,58 +3380,58 @@
         <v>-0</v>
       </c>
       <c r="O35" t="n">
-        <v>-0</v>
+        <v>4200</v>
       </c>
       <c r="P35" t="n">
         <v>-0</v>
       </c>
       <c r="Q35" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="R35" t="n">
         <v>-0</v>
       </c>
       <c r="S35" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T35" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W35" t="n">
         <v>12000</v>
       </c>
-      <c r="T35" t="n">
-        <v>-0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>-0</v>
-      </c>
-      <c r="V35" t="n">
+      <c r="X35" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y35" t="n">
         <v>4200</v>
       </c>
-      <c r="W35" t="n">
-        <v>6000</v>
-      </c>
-      <c r="X35" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>-0</v>
-      </c>
       <c r="Z35" t="n">
-        <v>4200</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S182</t>
+          <t>S266</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>-0</v>
       </c>
       <c r="D36" t="n">
-        <v>4200</v>
+        <v>-0</v>
       </c>
       <c r="E36" t="n">
         <v>-0</v>
@@ -3446,13 +3446,13 @@
         <v>-0</v>
       </c>
       <c r="I36" t="n">
-        <v>4200</v>
+        <v>-0</v>
       </c>
       <c r="J36" t="n">
         <v>-0</v>
       </c>
       <c r="K36" t="n">
-        <v>4200</v>
+        <v>-0</v>
       </c>
       <c r="L36" t="n">
         <v>-0</v>
@@ -3464,7 +3464,7 @@
         <v>-0</v>
       </c>
       <c r="O36" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="P36" t="n">
         <v>-0</v>
@@ -3488,7 +3488,7 @@
         <v>-0</v>
       </c>
       <c r="W36" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="X36" t="n">
         <v>-0</v>
@@ -3503,31 +3503,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S332</t>
+          <t>S362</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="D37" t="n">
         <v>-0</v>
       </c>
       <c r="E37" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="F37" t="n">
         <v>-0</v>
       </c>
       <c r="G37" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="H37" t="n">
-        <v>-0</v>
+        <v>12000</v>
       </c>
       <c r="I37" t="n">
         <v>-0</v>
@@ -3536,25 +3536,25 @@
         <v>-0</v>
       </c>
       <c r="K37" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="L37" t="n">
         <v>-0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0</v>
+        <v>12000</v>
       </c>
       <c r="N37" t="n">
         <v>-0</v>
       </c>
       <c r="O37" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="P37" t="n">
         <v>-0</v>
       </c>
       <c r="Q37" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="R37" t="n">
         <v>-0</v>
@@ -3572,7 +3572,7 @@
         <v>-0</v>
       </c>
       <c r="W37" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="X37" t="n">
         <v>-0</v>
@@ -3587,16 +3587,16 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S239</t>
+          <t>S332</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="D38" t="n">
         <v>-0</v>
@@ -3629,10 +3629,10 @@
         <v>-0</v>
       </c>
       <c r="N38" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="O38" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="P38" t="n">
         <v>-0</v>
@@ -3656,10 +3656,10 @@
         <v>-0</v>
       </c>
       <c r="W38" t="n">
-        <v>4200</v>
+        <v>-0</v>
       </c>
       <c r="X38" t="n">
-        <v>12000</v>
+        <v>-0</v>
       </c>
       <c r="Y38" t="n">
         <v>-0</v>
@@ -3671,7 +3671,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S175</t>
+          <t>S105</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3686,25 +3686,25 @@
         <v>-0</v>
       </c>
       <c r="E39" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="F39" t="n">
         <v>6000</v>
       </c>
       <c r="G39" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="H39" t="n">
         <v>-0</v>
       </c>
       <c r="I39" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="J39" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="K39" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="L39" t="n">
         <v>-0</v>
@@ -3713,19 +3713,19 @@
         <v>-0</v>
       </c>
       <c r="N39" t="n">
-        <v>4200</v>
+        <v>-0</v>
       </c>
       <c r="O39" t="n">
         <v>-0</v>
       </c>
       <c r="P39" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="Q39" t="n">
         <v>-0</v>
       </c>
       <c r="R39" t="n">
-        <v>-0</v>
+        <v>12000</v>
       </c>
       <c r="S39" t="n">
         <v>-0</v>
@@ -3734,7 +3734,7 @@
         <v>-0</v>
       </c>
       <c r="U39" t="n">
-        <v>4200</v>
+        <v>-0</v>
       </c>
       <c r="V39" t="n">
         <v>6000</v>
@@ -3743,24 +3743,24 @@
         <v>-0</v>
       </c>
       <c r="X39" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="Y39" t="n">
         <v>-0</v>
       </c>
       <c r="Z39" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S031</t>
+          <t>S301</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3782,10 +3782,10 @@
         <v>-0</v>
       </c>
       <c r="I40" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="J40" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="K40" t="n">
         <v>-0</v>
@@ -3797,7 +3797,7 @@
         <v>-0</v>
       </c>
       <c r="N40" t="n">
-        <v>-0</v>
+        <v>12000</v>
       </c>
       <c r="O40" t="n">
         <v>-0</v>
@@ -3821,13 +3821,13 @@
         <v>-0</v>
       </c>
       <c r="V40" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="W40" t="n">
-        <v>-0</v>
+        <v>4200</v>
       </c>
       <c r="X40" t="n">
-        <v>-0</v>
+        <v>12000</v>
       </c>
       <c r="Y40" t="n">
         <v>-0</v>
@@ -3839,12 +3839,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S037</t>
+          <t>S066</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3869,7 +3869,7 @@
         <v>-0</v>
       </c>
       <c r="J41" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="K41" t="n">
         <v>-0</v>
@@ -3881,19 +3881,19 @@
         <v>-0</v>
       </c>
       <c r="N41" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="O41" t="n">
         <v>-0</v>
       </c>
       <c r="P41" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="Q41" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="R41" t="n">
-        <v>4200</v>
+        <v>-0</v>
       </c>
       <c r="S41" t="n">
         <v>-0</v>
@@ -3911,7 +3911,7 @@
         <v>-0</v>
       </c>
       <c r="X41" t="n">
-        <v>10200</v>
+        <v>-0</v>
       </c>
       <c r="Y41" t="n">
         <v>-0</v>
@@ -3923,12 +3923,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S359</t>
+          <t>S054</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -4007,22 +4007,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S020</t>
+          <t>S385</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>-0</v>
       </c>
       <c r="D43" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="E43" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="F43" t="n">
         <v>-0</v>
@@ -4037,16 +4037,16 @@
         <v>-0</v>
       </c>
       <c r="J43" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="K43" t="n">
         <v>-0</v>
       </c>
       <c r="L43" t="n">
-        <v>-0</v>
+        <v>4200</v>
       </c>
       <c r="M43" t="n">
-        <v>-0</v>
+        <v>12000</v>
       </c>
       <c r="N43" t="n">
         <v>-0</v>
@@ -4061,7 +4061,7 @@
         <v>-0</v>
       </c>
       <c r="R43" t="n">
-        <v>-0</v>
+        <v>10200</v>
       </c>
       <c r="S43" t="n">
         <v>-0</v>
@@ -4070,7 +4070,7 @@
         <v>-0</v>
       </c>
       <c r="U43" t="n">
-        <v>-0</v>
+        <v>6000</v>
       </c>
       <c r="V43" t="n">
         <v>-0</v>
@@ -4091,7 +4091,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S158</t>
+          <t>S360</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4175,12 +4175,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S271</t>
+          <t>S227</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -4259,12 +4259,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S341</t>
+          <t>S076</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4343,12 +4343,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S198</t>
+          <t>S302</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4397,7 +4397,7 @@
         <v>-0</v>
       </c>
       <c r="R47" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="S47" t="n">
         <v>-0</v>
@@ -4412,7 +4412,7 @@
         <v>-0</v>
       </c>
       <c r="W47" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="X47" t="n">
         <v>-0</v>
@@ -4427,12 +4427,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S111</t>
+          <t>S389</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4451,7 +4451,7 @@
         <v>-0</v>
       </c>
       <c r="H48" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="I48" t="n">
         <v>-0</v>
@@ -4460,7 +4460,7 @@
         <v>-0</v>
       </c>
       <c r="K48" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="L48" t="n">
         <v>-0</v>
@@ -4505,18 +4505,18 @@
         <v>-0</v>
       </c>
       <c r="Z48" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S195</t>
+          <t>S396</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4529,7 +4529,7 @@
         <v>-0</v>
       </c>
       <c r="F49" t="n">
-        <v>10200</v>
+        <v>-0</v>
       </c>
       <c r="G49" t="n">
         <v>-0</v>
@@ -4538,10 +4538,10 @@
         <v>-0</v>
       </c>
       <c r="I49" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="J49" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="K49" t="n">
         <v>-0</v>
@@ -4574,7 +4574,7 @@
         <v>-0</v>
       </c>
       <c r="U49" t="n">
-        <v>6000</v>
+        <v>-0</v>
       </c>
       <c r="V49" t="n">
         <v>-0</v>
@@ -4586,7 +4586,7 @@
         <v>-0</v>
       </c>
       <c r="Y49" t="n">
-        <v>4200</v>
+        <v>-0</v>
       </c>
       <c r="Z49" t="n">
         <v>-0</v>
@@ -4595,12 +4595,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S068</t>
+          <t>S084</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4679,12 +4679,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S064</t>
+          <t>S214</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C51" t="n">
